--- a/BOM Format/BOM Template/PCBWay.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/PCBWay.Bom.Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60620BE9-11CD-481B-A71A-23E4E7D224C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85638526-DB2A-4975-8761-ED8E1C3A48F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Component list</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Column=LCSC/MOQ/(  Boards)</t>
+  </si>
+  <si>
+    <t>Column=Item Type</t>
   </si>
 </sst>
 </file>
@@ -259,7 +262,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -517,11 +520,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -678,6 +692,32 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -706,13 +746,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -743,7 +783,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20059650" y="629542"/>
+          <a:off x="17506950" y="629542"/>
           <a:ext cx="1857375" cy="1104008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1020,275 +1060,292 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" customWidth="1"/>
-    <col min="9" max="9" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" customWidth="1"/>
+    <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="22"/>
-      <c r="C1" s="2"/>
+      <c r="C1" s="22"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="57"/>
+      <c r="I1" s="2"/>
       <c r="J1" s="57"/>
       <c r="K1" s="57"/>
       <c r="L1" s="57"/>
-    </row>
-    <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M1" s="57"/>
+    </row>
+    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="23"/>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="60"/>
+      <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="3"/>
+      <c r="G2" s="11"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="54"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L2" s="3"/>
+      <c r="M2" s="54"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="24"/>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="61"/>
+      <c r="D3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="4"/>
+      <c r="G3" s="12"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="58"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L3" s="4"/>
+      <c r="M3" s="58"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="24"/>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="61"/>
+      <c r="D4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12"/>
+      <c r="F4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="6"/>
+      <c r="G4" s="15"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="59"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="6"/>
+      <c r="M4" s="59"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="24"/>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="61"/>
+      <c r="D5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="12"/>
+      <c r="F5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="5"/>
+      <c r="G5" s="17"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="59"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L5" s="5"/>
+      <c r="M5" s="59"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="25"/>
-      <c r="C6" s="18"/>
+      <c r="C6" s="62"/>
       <c r="D6" s="18"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="5"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="17"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="59"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="5"/>
+      <c r="M6" s="59"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="26"/>
-      <c r="C7" s="20"/>
+      <c r="C7" s="63"/>
       <c r="D7" s="20"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="7"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="20"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="59"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="7"/>
+      <c r="M7" s="59"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
+      <c r="C8" s="64"/>
       <c r="D8" s="30"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="7"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="20"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="59"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="7"/>
+      <c r="M8" s="59"/>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="32" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="F9" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="G9" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="H9" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="I9" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="33" t="s">
+      <c r="J9" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="K9" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="32" t="s">
+      <c r="L9" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="34" t="s">
+      <c r="M9" s="34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="35">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="42"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
       <c r="H10" s="42"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
       <c r="K10" s="42"/>
-      <c r="L10" s="50"/>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="42"/>
+      <c r="M10" s="50"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="35">
         <f t="shared" ref="B11:B13" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="44"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="45"/>
       <c r="H11" s="44"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="45"/>
       <c r="K11" s="44"/>
-      <c r="L11" s="51"/>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="44"/>
+      <c r="M11" s="51"/>
+    </row>
+    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="35">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="46"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="47"/>
       <c r="H12" s="46"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="47"/>
       <c r="K12" s="46"/>
-      <c r="L12" s="52"/>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="46"/>
+      <c r="M12" s="52"/>
+    </row>
+    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="36">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="48"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="49"/>
       <c r="H13" s="48"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="49"/>
       <c r="K13" s="48"/>
-      <c r="L13" s="53"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L13" s="48"/>
+      <c r="M13" s="53"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="37"/>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="66"/>
+      <c r="D14" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="40"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
       <c r="H14" s="40"/>
-      <c r="I14" s="41"/>
+      <c r="I14" s="40"/>
       <c r="J14" s="41"/>
       <c r="K14" s="41"/>
-      <c r="L14" s="55"/>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="41"/>
+      <c r="M14" s="55"/>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="67"/>
+      <c r="D15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
@@ -1296,12 +1353,13 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="56"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="L3:L8"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="M3:M8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BOM Format/BOM Template/PCBWay.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/PCBWay.Bom.Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85638526-DB2A-4975-8761-ED8E1C3A48F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651C6785-97F2-462B-8460-78E2ADC4C64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,13 +89,13 @@
     <t>Column=Remarks</t>
   </si>
   <si>
-    <t>Column=LCSC/Part No</t>
-  </si>
-  <si>
     <t>Column=LCSC/MOQ/(  Boards)</t>
   </si>
   <si>
     <t>Column=Item Type</t>
+  </si>
+  <si>
+    <t>Column=LCSC/Part Number</t>
   </si>
 </sst>
 </file>
@@ -262,7 +262,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -425,16 +425,29 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -445,9 +458,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -457,56 +468,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -535,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -618,12 +579,6 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -640,59 +595,41 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -708,7 +645,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -718,6 +655,18 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1060,7 +1009,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="28" customWidth="1"/>
@@ -1070,7 +1019,7 @@
     <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="29.42578125" customWidth="1"/>
   </cols>
@@ -1085,15 +1034,15 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
     </row>
     <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="23"/>
-      <c r="C2" s="60"/>
+      <c r="C2" s="52"/>
       <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
@@ -1107,12 +1056,12 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="54"/>
+      <c r="M2" s="49"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="24"/>
-      <c r="C3" s="61"/>
+      <c r="C3" s="53"/>
       <c r="D3" s="12" t="s">
         <v>2</v>
       </c>
@@ -1126,12 +1075,12 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
-      <c r="M3" s="58"/>
+      <c r="M3" s="61"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="24"/>
-      <c r="C4" s="61"/>
+      <c r="C4" s="53"/>
       <c r="D4" s="12" t="s">
         <v>4</v>
       </c>
@@ -1145,12 +1094,12 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="59"/>
+      <c r="M4" s="62"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="24"/>
-      <c r="C5" s="61"/>
+      <c r="C5" s="53"/>
       <c r="D5" s="12" t="s">
         <v>6</v>
       </c>
@@ -1164,12 +1113,12 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="59"/>
+      <c r="M5" s="62"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="25"/>
-      <c r="C6" s="62"/>
+      <c r="C6" s="54"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
@@ -1179,12 +1128,12 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="59"/>
+      <c r="M6" s="62"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="26"/>
-      <c r="C7" s="63"/>
+      <c r="C7" s="55"/>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="F7" s="21"/>
@@ -1194,12 +1143,12 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="59"/>
+      <c r="M7" s="62"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="29"/>
-      <c r="C8" s="64"/>
+      <c r="C8" s="56"/>
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
       <c r="F8" s="31"/>
@@ -1209,7 +1158,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="59"/>
+      <c r="M8" s="62"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1217,7 +1166,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>13</v>
@@ -1235,7 +1184,7 @@
         <v>16</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J9" s="33" t="s">
         <v>17</v>
@@ -1244,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M9" s="34" t="s">
         <v>18</v>
@@ -1252,109 +1201,91 @@
     </row>
     <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="35">
+      <c r="B10" s="63">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="50"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="46"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="35">
-        <f t="shared" ref="B11:B13" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="63">
+        <f t="shared" ref="B11:B12" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="51"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="47"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="35">
+      <c r="B12" s="63">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="52"/>
-    </row>
-    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="57"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="48"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="36">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="48"/>
-      <c r="M13" s="53"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="35"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="37"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="50"/>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="55"/>
-    </row>
-    <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="8" t="s">
+      <c r="B14" s="27"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="56"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/BOM Format/BOM Template/PCBWay.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/PCBWay.Bom.Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651C6785-97F2-462B-8460-78E2ADC4C64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B1A377-6724-494F-8EF0-42EA92D874B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Component list</t>
   </si>
@@ -63,12 +63,6 @@
   </si>
   <si>
     <t>Column=Quantity</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Column=Designator</t>
@@ -262,7 +256,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -481,22 +475,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -645,9 +628,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -656,6 +636,9 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -664,9 +647,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1166,46 +1146,46 @@
         <v>8</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="I9" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="33" t="s">
         <v>15</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="33" t="s">
-        <v>17</v>
       </c>
       <c r="K9" s="32" t="s">
         <v>10</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M9" s="34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="63">
+      <c r="B10" s="59">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="57"/>
+      <c r="C10" s="40"/>
       <c r="D10" s="40"/>
       <c r="E10" s="41"/>
       <c r="F10" s="40"/>
@@ -1219,11 +1199,11 @@
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="63">
+      <c r="B11" s="59">
         <f t="shared" ref="B11:B12" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="57"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="42"/>
       <c r="E11" s="43"/>
       <c r="F11" s="42"/>
@@ -1237,11 +1217,11 @@
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="63">
+      <c r="B12" s="59">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="57"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="44"/>
       <c r="E12" s="45"/>
       <c r="F12" s="44"/>
@@ -1256,10 +1236,8 @@
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="35"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="36" t="s">
-        <v>11</v>
-      </c>
+      <c r="C13" s="57"/>
+      <c r="D13" s="36"/>
       <c r="E13" s="37"/>
       <c r="F13" s="38"/>
       <c r="G13" s="39"/>
@@ -1273,10 +1251,8 @@
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="8" t="s">
-        <v>12</v>
-      </c>
+      <c r="C14" s="58"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>

--- a/BOM Format/BOM Template/PCBWay.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/PCBWay.Bom.Template.xlsx
@@ -1,36 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B1A377-6724-494F-8EF0-42EA92D874B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FDEA03-A15D-4875-99A5-02C005008651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Component list</t>
   </si>
@@ -62,9 +52,6 @@
     <t>Column=Description</t>
   </si>
   <si>
-    <t>Column=Quantity</t>
-  </si>
-  <si>
     <t>Column=Designator</t>
   </si>
   <si>
@@ -83,13 +70,19 @@
     <t>Column=Remarks</t>
   </si>
   <si>
-    <t>Column=LCSC/MOQ/(  Boards)</t>
-  </si>
-  <si>
     <t>Column=Item Type</t>
   </si>
   <si>
-    <t>Column=LCSC/Part Number</t>
+    <t>Column=LCSC Part Number</t>
+  </si>
+  <si>
+    <t>Column=Quantity (1 Board)</t>
+  </si>
+  <si>
+    <t>Column=Quantity (  Board)</t>
+  </si>
+  <si>
+    <t>Column=MOQ (   Boards)</t>
   </si>
 </sst>
 </file>
@@ -481,20 +474,20 @@
   </cellStyleXfs>
   <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -504,27 +497,27 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -539,7 +532,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -549,8 +542,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -562,22 +555,22 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -608,31 +601,31 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -675,13 +668,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -989,7 +982,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="28" customWidth="1"/>
@@ -1001,10 +994,10 @@
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="29.42578125" customWidth="1"/>
+    <col min="11" max="14" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -1018,8 +1011,9 @@
       <c r="K1" s="60"/>
       <c r="L1" s="60"/>
       <c r="M1" s="60"/>
-    </row>
-    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N1" s="60"/>
+    </row>
+    <row r="2" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="23"/>
       <c r="C2" s="52"/>
@@ -1036,9 +1030,10 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="49"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M2" s="3"/>
+      <c r="N2" s="49"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="24"/>
       <c r="C3" s="53"/>
@@ -1055,9 +1050,10 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
-      <c r="M3" s="61"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M3" s="4"/>
+      <c r="N3" s="61"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="24"/>
       <c r="C4" s="53"/>
@@ -1074,9 +1070,10 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="62"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M4" s="6"/>
+      <c r="N4" s="62"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="24"/>
       <c r="C5" s="53"/>
@@ -1093,9 +1090,10 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="62"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M5" s="5"/>
+      <c r="N5" s="62"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="25"/>
       <c r="C6" s="54"/>
@@ -1108,9 +1106,10 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="62"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M6" s="5"/>
+      <c r="N6" s="62"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="26"/>
       <c r="C7" s="55"/>
@@ -1123,9 +1122,10 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="62"/>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="7"/>
+      <c r="N7" s="62"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="29"/>
       <c r="C8" s="56"/>
@@ -1138,48 +1138,52 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="62"/>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="7"/>
+      <c r="N8" s="62"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="32" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="H9" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="I9" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="K9" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="M9" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9" s="34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="59">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -1195,9 +1199,10 @@
       <c r="J10" s="41"/>
       <c r="K10" s="40"/>
       <c r="L10" s="40"/>
-      <c r="M10" s="46"/>
-    </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="40"/>
+      <c r="N10" s="46"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="59">
         <f t="shared" ref="B11:B12" si="0">ROW(B11) - ROW($B$9)</f>
@@ -1213,9 +1218,10 @@
       <c r="J11" s="43"/>
       <c r="K11" s="42"/>
       <c r="L11" s="42"/>
-      <c r="M11" s="47"/>
-    </row>
-    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="42"/>
+      <c r="N11" s="47"/>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="59">
         <f t="shared" si="0"/>
@@ -1231,9 +1237,10 @@
       <c r="J12" s="45"/>
       <c r="K12" s="44"/>
       <c r="L12" s="44"/>
-      <c r="M12" s="48"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M12" s="44"/>
+      <c r="N12" s="48"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="35"/>
       <c r="C13" s="57"/>
@@ -1246,9 +1253,10 @@
       <c r="J13" s="39"/>
       <c r="K13" s="39"/>
       <c r="L13" s="39"/>
-      <c r="M13" s="50"/>
-    </row>
-    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="39"/>
+      <c r="N13" s="50"/>
+    </row>
+    <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="27"/>
       <c r="C14" s="58"/>
@@ -1261,12 +1269,13 @@
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
-      <c r="M14" s="51"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="M3:M8"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="N3:N8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
